--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488137_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488137_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6662</v>
+        <v>0.9162</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.95</v>
+        <v>-1.6015</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6163</v>
+        <v>2.5178</v>
       </c>
       <c r="G3" t="n">
         <v>1.2178</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.3274</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.858</v>
+        <v>-0.5095</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9354</v>
+        <v>0.8369</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6289</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6187</v>
+        <v>0.3807</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2635</v>
+        <v>-0.1715</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3552</v>
+        <v>0.5522</v>
       </c>
       <c r="G4" t="n">
         <v>2.4806</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1947</v>
+        <v>-0.0432</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1169</v>
+        <v>-0.5518</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3116</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-0.945</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4587</v>
+        <v>-1.1633</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.2111</v>
+        <v>-2.0394</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7524</v>
+        <v>0.8761</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5633</v>
+        <v>-1.2771</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3562</v>
+        <v>-0.2095</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7929</v>
+        <v>-1.0676</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9968</v>
+        <v>-1.2628</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1212</v>
+        <v>0.0429</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1244</v>
+        <v>-1.3057</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4335</v>
+        <v>-0.0143</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.235</v>
+        <v>-0.2524</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6685</v>
+        <v>0.2381</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.2234</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6987</v>
+        <v>0.4844</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2326</v>
+        <v>0.1499</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4661</v>
+        <v>0.3345</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9182</v>
+        <v>-1.2701</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8435</v>
+        <v>-3.407</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9253</v>
+        <v>2.1369</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2771</v>
+        <v>-0.5633</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2095</v>
+        <v>-1.3562</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0676</v>
+        <v>0.7929</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2628</v>
+        <v>-0.9968</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0429</v>
+        <v>-1.1212</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3057</v>
+        <v>0.1244</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0143</v>
+        <v>0.4335</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2524</v>
+        <v>-0.235</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2381</v>
+        <v>0.6685</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3706</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7295</v>
+        <v>0.8873</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3457</v>
+        <v>0.0367</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3837</v>
+        <v>0.8505</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2504</v>
+        <v>-1.7088</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8541</v>
+        <v>-1.9946</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6037</v>
+        <v>0.2858</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.313</v>
+        <v>-0.755</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.608</v>
+        <v>0.2432</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.705</v>
+        <v>-0.9982</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.415</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.8865</v>
+        <v>1.4299</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5284</v>
+        <v>-0.4455</v>
       </c>
       <c r="M7" t="n">
-        <v>0.102</v>
+        <v>-1.7394</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2786</v>
+        <v>-1.1867</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1766</v>
+        <v>-0.5527</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1117</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9508</v>
+        <v>-0.3979</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5609</v>
+        <v>-0.4961</v>
       </c>
       <c r="U7" t="n">
-        <v>0.39</v>
+        <v>0.0982</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0098</v>
+        <v>-1.7641</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0494</v>
+        <v>-3.4417</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0396</v>
+        <v>1.6776</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.755</v>
+        <v>-3.313</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2432</v>
+        <v>-2.608</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9982</v>
+        <v>-0.705</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9844000000000001</v>
+        <v>-3.415</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4299</v>
+        <v>-2.8865</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4455</v>
+        <v>-0.5284</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7394</v>
+        <v>0.102</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1867</v>
+        <v>0.2786</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5527</v>
+        <v>-0.1766</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6989</v>
+        <v>0.4371</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.0267</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.148</v>
+        <v>0.4638</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8792</v>
+        <v>-2.2401</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6601</v>
+        <v>-2.4642</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2191</v>
+        <v>0.2241</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3727</v>
@@ -1156,13 +1156,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2094</v>
+        <v>0.4296</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0373</v>
+        <v>0.1586</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1721</v>
+        <v>0.2711</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. CATALDO</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1072</v>
+        <v>-3.1048</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5014</v>
+        <v>-3.14</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6058</v>
+        <v>0.0351</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6628</v>
+        <v>-3.4458</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3004</v>
+        <v>-1.3492</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3624</v>
+        <v>-2.0966</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0678</v>
+        <v>-1.9068</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5808</v>
+        <v>-0.1248</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.487</v>
+        <v>-1.782</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.595</v>
+        <v>-1.5389</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7196</v>
+        <v>-1.2244</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8754</v>
+        <v>-0.3145</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7411</v>
+        <v>1.8529</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1109</v>
+        <v>-0.2885</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.766</v>
+        <v>-0.6392</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8769</v>
+        <v>0.3506</v>
       </c>
       <c r="V10" t="n">
-        <v>0.63</v>
+        <v>0.6294</v>
       </c>
       <c r="W10" t="n">
         <v>1.2589</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6289</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>B. CATALDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0907</v>
+        <v>-3.2013</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9781</v>
+        <v>-2.2508</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1126</v>
+        <v>-0.9505</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4458</v>
+        <v>-3.6628</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3492</v>
+        <v>-2.3004</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0966</v>
+        <v>-1.3624</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9068</v>
+        <v>-2.0678</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1248</v>
+        <v>-1.5808</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.782</v>
+        <v>-0.487</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5389</v>
+        <v>-1.595</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2244</v>
+        <v>-0.7196</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3145</v>
+        <v>-0.8754</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2744</v>
+        <v>0.0168</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4773</v>
+        <v>-0.5154</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2029</v>
+        <v>0.5322</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6294</v>
+        <v>0.63</v>
       </c>
       <c r="W11" t="n">
         <v>1.2589</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6294</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.4852</v>
+        <v>-12.2115</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.8401</v>
+        <v>-19.5666</v>
       </c>
       <c r="F12" t="n">
-        <v>7.355</v>
+        <v>7.3551</v>
       </c>
       <c r="G12" t="n">
         <v>-9.747199999999999</v>
@@ -1360,22 +1360,22 @@
         <v>-9.517199999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2300000000000004</v>
+        <v>-0.23</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.939499999999999</v>
+        <v>-3.9395</v>
       </c>
       <c r="K12" t="n">
         <v>-4.7443</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.8048999999999996</v>
       </c>
       <c r="M12" t="n">
         <v>-5.8075</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.772699999999999</v>
+        <v>-4.7727</v>
       </c>
       <c r="O12" t="n">
         <v>-1.0348</v>
@@ -1390,16 +1390,16 @@
         <v>11.1173</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5792</v>
+        <v>1.853</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.6672</v>
+        <v>-2.3935</v>
       </c>
       <c r="U12" t="n">
-        <v>4.246499999999999</v>
+        <v>4.2464</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3149</v>
+        <v>0.3148999999999998</v>
       </c>
       <c r="W12" t="n">
         <v>2.5162</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5663</v>
+        <v>6.2867</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2887</v>
+        <v>1.3483</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2776</v>
+        <v>4.9385</v>
       </c>
       <c r="G13" t="n">
-        <v>5.2244</v>
+        <v>6.3331</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4563</v>
+        <v>3.4117</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7681</v>
+        <v>2.9215</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6834</v>
+        <v>4.4495</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5162</v>
+        <v>2.3961</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1672</v>
+        <v>2.0535</v>
       </c>
       <c r="M13" t="n">
-        <v>0.541</v>
+        <v>1.8836</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9402</v>
+        <v>1.0156</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3991</v>
+        <v>0.868</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9264</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7793</v>
+        <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7309</v>
+        <v>-0.2496</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2263</v>
+        <v>-0.6364</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.3867</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3155</v>
+        <v>0.9444</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3155</v>
+        <v>0.3144</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5669</v>
+        <v>6.2553</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0545</v>
+        <v>1.9949</v>
       </c>
       <c r="F14" t="n">
-        <v>4.5124</v>
+        <v>4.2604</v>
       </c>
       <c r="G14" t="n">
-        <v>6.3331</v>
+        <v>5.2244</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4117</v>
+        <v>3.4563</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9215</v>
+        <v>1.7681</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4495</v>
+        <v>4.6834</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3961</v>
+        <v>2.5162</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0535</v>
+        <v>2.1672</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8836</v>
+        <v>0.541</v>
       </c>
       <c r="N14" t="n">
-        <v>1.0156</v>
+        <v>0.9402</v>
       </c>
       <c r="O14" t="n">
-        <v>0.868</v>
+        <v>-0.3991</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0382</v>
+        <v>2.7793</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9695</v>
+        <v>0.42</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9302</v>
+        <v>-0.5201</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0393</v>
+        <v>0.9401</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9444</v>
+        <v>-0.3155</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3144</v>
+        <v>-0.3155</v>
       </c>
       <c r="X14" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3889</v>
+        <v>3.6376</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2898</v>
+        <v>-1.0732</v>
       </c>
       <c r="F15" t="n">
-        <v>4.6787</v>
+        <v>4.7108</v>
       </c>
       <c r="G15" t="n">
         <v>2.7126</v>
@@ -1624,13 +1624,13 @@
         <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8061</v>
+        <v>0.0547</v>
       </c>
       <c r="T15" t="n">
-        <v>0.536</v>
+        <v>-0.2474</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2701</v>
+        <v>0.3021</v>
       </c>
       <c r="V15" t="n">
         <v>0.3144</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6263</v>
+        <v>1.4293</v>
       </c>
       <c r="E17" t="n">
         <v>-1.7799</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4062</v>
+        <v>3.2092</v>
       </c>
       <c r="G17" t="n">
         <v>0.8399</v>
@@ -1780,13 +1780,13 @@
         <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0453</v>
+        <v>-0.1517</v>
       </c>
       <c r="T17" t="n">
         <v>-0.332</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3773</v>
+        <v>0.1803</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2776</v>
+        <v>0.3022</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0547</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3323</v>
+        <v>0.3569</v>
       </c>
       <c r="G18" t="n">
         <v>0.1306</v>
@@ -1858,13 +1858,13 @@
         <v>0.1853</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0383</v>
+        <v>-0.0137</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2689</v>
+        <v>0.0747</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.601</v>
+        <v>-3.4051</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3321</v>
+        <v>3.4798</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4088</v>
@@ -1936,13 +1936,13 @@
         <v>2.7793</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7309</v>
+        <v>-0.3874</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9339</v>
+        <v>-0.738</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2029</v>
+        <v>0.3506</v>
       </c>
       <c r="V19" t="n">
         <v>0.9444</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4987</v>
+        <v>-0.2215</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8369</v>
+        <v>-1.641</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3382</v>
+        <v>1.4195</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6636</v>
@@ -2014,13 +2014,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.391</v>
+        <v>-0.1138</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7113</v>
+        <v>-0.5154</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3203</v>
+        <v>0.4016</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5134</v>
+        <v>-0.4802</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.426</v>
+        <v>-0.6218</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.1416</v>
       </c>
       <c r="G21" t="n">
         <v>0.9156</v>
@@ -2092,13 +2092,13 @@
         <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0532</v>
+        <v>0.0864</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1057</v>
+        <v>-0.0901</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0525</v>
+        <v>0.1766</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.884</v>
+        <v>-1.0799</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4321</v>
+        <v>-0.6279</v>
       </c>
       <c r="F22" t="n">
         <v>-0.452</v>
@@ -2170,10 +2170,10 @@
         <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1094</v>
+        <v>-0.3053</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0037</v>
+        <v>-0.1996</v>
       </c>
       <c r="U22" t="n">
         <v>-0.1057</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.647</v>
+        <v>-1.5983</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7029</v>
+        <v>-0.605</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.9933</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1512</v>
@@ -2248,13 +2248,13 @@
         <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0219</v>
+        <v>0.0706</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2407</v>
+        <v>0.1915</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2589</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2614</v>
+        <v>-4.6005</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7076</v>
+        <v>-4.0221</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5538</v>
+        <v>-0.5784</v>
       </c>
       <c r="G24" t="n">
         <v>-5.8758</v>
@@ -2326,13 +2326,13 @@
         <v>1.297</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9976</v>
+        <v>-0.3367</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4773</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4797</v>
+        <v>0.4551</v>
       </c>
       <c r="V24" t="n">
         <v>0.315</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>12.485</v>
+        <v>13.1378</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.3553</v>
+        <v>-7.3551</v>
       </c>
       <c r="F25" t="n">
-        <v>19.8401</v>
+        <v>20.493</v>
       </c>
       <c r="G25" t="n">
         <v>9.747000000000005</v>
@@ -2404,13 +2404,13 @@
         <v>15.7494</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5793</v>
+        <v>-0.9265</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.2466</v>
+        <v>-4.2464</v>
       </c>
       <c r="U25" t="n">
-        <v>2.6671</v>
+        <v>3.3199</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3150999999999997</v>
